--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -824,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W5" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -906,21 +906,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.30402</v>
+        <v>46.29559</v>
       </c>
       <c r="W6" t="n">
-        <v>-81.53989</v>
+        <v>-83.20277</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -988,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1053,14 +1053,14 @@
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.63956</v>
+        <v>46.30402</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.55477999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1299,14 +1299,14 @@
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1316,35 +1316,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>46.23809</v>
+        <v>45.58868</v>
       </c>
       <c r="W11" t="n">
-        <v>-82.11991</v>
+        <v>-79.70944</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1398,21 +1398,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.8</v>
+        <v>5.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1421,12 +1421,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.5143</v>
+        <v>49.71016</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61444</v>
+        <v>-94.40097</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1480,21 +1480,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.49976</v>
+        <v>44.52895</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1562,30 +1562,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>48.69799</v>
+        <v>44.5021</v>
       </c>
       <c r="W14" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1644,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>48.69799</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1726,35 +1726,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>45.58868</v>
+        <v>44.51686</v>
       </c>
       <c r="W16" t="n">
-        <v>-79.70944</v>
+        <v>-77.62098</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1808,12 +1808,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1822,7 +1822,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1864,23 +1864,105 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>44.5021</v>
+        <v>44.49976</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.61301</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>12</v>
+      </c>
+      <c r="T18" t="n">
+        <v>300</v>
+      </c>
+      <c r="U18" t="n">
+        <v>42</v>
+      </c>
+      <c r="V18" t="n">
+        <v>48.24876</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-89.86754000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -880,10 +880,10 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
@@ -906,21 +906,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.29559</v>
+        <v>46.30402</v>
       </c>
       <c r="W6" t="n">
-        <v>-83.20277</v>
+        <v>-81.53989</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -988,21 +988,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>46.30402</v>
+        <v>46.29559</v>
       </c>
       <c r="W7" t="n">
-        <v>-81.53989</v>
+        <v>-83.20277</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1208,10 +1208,10 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
@@ -1316,35 +1316,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1381,14 +1381,14 @@
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>45.58868</v>
+        <v>44.49976</v>
       </c>
       <c r="W11" t="n">
-        <v>-79.70944</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1398,35 +1398,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>49.71016</v>
+        <v>46.23809</v>
       </c>
       <c r="W12" t="n">
-        <v>-94.40097</v>
+        <v>-82.11991</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1480,21 +1480,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.52895</v>
+        <v>44.5021</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.78169</v>
+        <v>-77.61301</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1562,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.5021</v>
+        <v>45.58868</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61301</v>
+        <v>-79.70944</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1644,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>48.69799</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1782,10 +1782,10 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
@@ -1808,30 +1808,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,23 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>44.49976</v>
+        <v>48.69799</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.61284999999999</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1946,10 +1946,10 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
         <v>42</v>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -804,17 +800,17 @@
         <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>44.55039</v>
+        <v>46.30402</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.36235000000001</v>
+        <v>-81.53989</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -824,30 +820,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +865,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +876,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -906,30 +902,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -988,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.9</v>
+        <v>7.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1040,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>46.29559</v>
+        <v>44.73856</v>
       </c>
       <c r="W7" t="n">
-        <v>-83.20277</v>
+        <v>-76.32056</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1148,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1171,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1204,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1230,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1279,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>44.55883</v>
+        <v>49.71016</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.57349000000001</v>
+        <v>-94.40097</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,10 +1368,10 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
@@ -1398,30 +1394,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>46.23809</v>
+        <v>44.52895</v>
       </c>
       <c r="W12" t="n">
-        <v>-82.11991</v>
+        <v>-77.78169</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1480,30 +1476,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.5021</v>
+        <v>48.69799</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61301</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1644,21 +1640,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1667,7 +1663,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1685,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1696,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>44.5021</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-77.61301</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1726,35 +1722,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,185 +1778,21 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V16" t="n">
-        <v>44.51686</v>
+        <v>48.24876</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.62098</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X16" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Reef Point Occurrence</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MDI52C11NW00007</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Windy Point</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Copper, Nickel</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>13</v>
-      </c>
-      <c r="T17" t="n">
-        <v>325</v>
-      </c>
-      <c r="U17" t="n">
-        <v>43</v>
-      </c>
-      <c r="V17" t="n">
-        <v>48.69799</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-93.27513999999999</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>13</v>
-      </c>
-      <c r="T18" t="n">
-        <v>325</v>
-      </c>
-      <c r="U18" t="n">
-        <v>42</v>
-      </c>
-      <c r="V18" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X18" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,10 +780,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Au 1120g/t, Cu 0.66%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -800,17 +804,17 @@
         <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>46.30402</v>
+        <v>44.55039</v>
       </c>
       <c r="W4" t="n">
-        <v>-81.53989</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -820,21 +824,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -843,7 +847,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -865,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -876,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.29559</v>
+        <v>46.30402</v>
       </c>
       <c r="W5" t="n">
-        <v>-83.20277</v>
+        <v>-81.53989</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -902,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T6" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -984,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7.7</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1040,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.73856</v>
+        <v>44.63956</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.32056</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1111,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1122,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.62168</v>
+        <v>44.73856</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.56963</v>
+        <v>-76.32056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1148,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1193,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1213,14 +1217,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1230,35 +1234,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.7</v>
+        <v>4.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>49.71016</v>
+        <v>44.55883</v>
       </c>
       <c r="W10" t="n">
-        <v>-94.40097</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1312,21 +1316,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.49976</v>
+        <v>44.52895</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1394,30 +1398,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1439,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.52895</v>
+        <v>46.23809</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.78169</v>
+        <v>-82.11991</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1476,35 +1480,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1521,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>48.69799</v>
+        <v>45.58868</v>
       </c>
       <c r="W13" t="n">
-        <v>-93.27513999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1558,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1603,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>45.58868</v>
+        <v>49.71016</v>
       </c>
       <c r="W14" t="n">
-        <v>-79.70944</v>
+        <v>-94.40097</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1722,35 +1726,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1767,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,23 +1782,187 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>48.24876</v>
+        <v>44.49976</v>
       </c>
       <c r="W16" t="n">
-        <v>-89.86754000000001</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Reef Point Occurrence</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MDI52C11NW00007</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Windy Point</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T17" t="n">
+        <v>300</v>
+      </c>
+      <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>48.69799</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-93.27513999999999</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Hawk Eye</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI31C12SE00032</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deloro</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>225</v>
+      </c>
+      <c r="U18" t="n">
+        <v>43</v>
+      </c>
+      <c r="V18" t="n">
+        <v>44.51686</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-77.62098</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
         <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -824,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W5" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -988,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1053,14 +1053,14 @@
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.63956</v>
+        <v>46.30402</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.55477999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1217,14 +1217,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1299,14 +1299,14 @@
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1316,21 +1316,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.52895</v>
+        <v>44.49976</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.78169</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1398,30 +1398,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>46.23809</v>
+        <v>44.5021</v>
       </c>
       <c r="W12" t="n">
-        <v>-82.11991</v>
+        <v>-77.61301</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1480,35 +1480,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>45.58868</v>
+        <v>44.52895</v>
       </c>
       <c r="W13" t="n">
-        <v>-79.70944</v>
+        <v>-77.78169</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1562,21 +1562,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.7</v>
+        <v>0.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>49.71016</v>
+        <v>44.51686</v>
       </c>
       <c r="W14" t="n">
-        <v>-94.40097</v>
+        <v>-77.62098</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1644,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.5021</v>
+        <v>48.69799</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.61301</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1726,35 +1726,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.49976</v>
+        <v>45.58868</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61284999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1808,21 +1808,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,23 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>48.69799</v>
+        <v>46.23809</v>
       </c>
       <c r="W17" t="n">
-        <v>-93.27513999999999</v>
+        <v>-82.11991</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1890,35 +1890,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.6</v>
+        <v>2.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1935,7 +1935,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1946,23 +1946,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V18" t="n">
-        <v>44.51686</v>
+        <v>48.24876</v>
       </c>
       <c r="W18" t="n">
-        <v>-77.62098</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -824,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -906,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1070,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1299,14 +1299,14 @@
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1316,21 +1316,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.49976</v>
+        <v>49.71016</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61284999999999</v>
+        <v>-94.40097</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.5021</v>
+        <v>44.51686</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61301</v>
+        <v>-77.62098</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1480,30 +1480,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.52895</v>
+        <v>48.69799</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.78169</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1562,30 +1562,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6</v>
+        <v>4.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.51686</v>
+        <v>46.23809</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.62098</v>
+        <v>-82.11991</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1644,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1709,14 +1709,14 @@
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>48.69799</v>
+        <v>44.5021</v>
       </c>
       <c r="W15" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1726,35 +1726,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1791,14 +1791,14 @@
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>45.58868</v>
+        <v>44.49976</v>
       </c>
       <c r="W16" t="n">
-        <v>-79.70944</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1808,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,23 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>46.23809</v>
+        <v>45.58868</v>
       </c>
       <c r="W17" t="n">
-        <v>-82.11991</v>
+        <v>-79.70944</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1890,35 +1890,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1935,7 +1935,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1946,23 +1946,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V18" t="n">
-        <v>48.24876</v>
+        <v>44.52895</v>
       </c>
       <c r="W18" t="n">
-        <v>-89.86754000000001</v>
+        <v>-77.78169</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>44.55039</v>
+        <v>46.29559</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20277</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -824,21 +820,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -847,7 +843,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +865,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +876,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.29559</v>
+        <v>46.30402</v>
       </c>
       <c r="W5" t="n">
-        <v>-83.20277</v>
+        <v>-81.53989</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -962,10 +958,10 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
@@ -988,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1040,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>46.30402</v>
+        <v>44.73856</v>
       </c>
       <c r="W7" t="n">
-        <v>-81.53989</v>
+        <v>-76.32056</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1148,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1171,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1204,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1230,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1279,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>44.55883</v>
+        <v>49.71016</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.57349000000001</v>
+        <v>-94.40097</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1316,21 +1312,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1339,12 +1335,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>49.71016</v>
+        <v>44.52895</v>
       </c>
       <c r="W11" t="n">
-        <v>-94.40097</v>
+        <v>-77.78169</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1398,30 +1394,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.51686</v>
+        <v>48.69799</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.62098</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1480,30 +1476,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1545,14 +1541,14 @@
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>48.69799</v>
+        <v>44.5021</v>
       </c>
       <c r="W13" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1562,35 +1558,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1607,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1614,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>46.23809</v>
+        <v>45.58868</v>
       </c>
       <c r="W14" t="n">
-        <v>-82.11991</v>
+        <v>-79.70944</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1640,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1658,7 +1654,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1667,7 +1663,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1685,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,269 +1696,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.5021</v>
+        <v>44.49976</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.61301</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ackerman</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MDI31C05NE00018</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Deloro</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>13</v>
-      </c>
-      <c r="T16" t="n">
-        <v>325</v>
-      </c>
-      <c r="U16" t="n">
-        <v>43</v>
-      </c>
-      <c r="V16" t="n">
-        <v>44.49976</v>
-      </c>
-      <c r="W16" t="n">
-        <v>-77.61284999999999</v>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Rock Brook Resources Property</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MDI31E12SE00004</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Oranmore</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Calcite</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>13</v>
-      </c>
-      <c r="T17" t="n">
-        <v>325</v>
-      </c>
-      <c r="U17" t="n">
-        <v>43</v>
-      </c>
-      <c r="V17" t="n">
-        <v>45.58868</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-79.70944</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ledyard</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI31C12SW00008</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Cordova Mines</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>9</v>
-      </c>
-      <c r="T18" t="n">
-        <v>225</v>
-      </c>
-      <c r="U18" t="n">
-        <v>43</v>
-      </c>
-      <c r="V18" t="n">
-        <v>44.52895</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-77.78169</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,10 +780,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -794,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>46.29559</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20277</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -820,21 +824,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -843,7 +847,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -865,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -876,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.30402</v>
+        <v>46.29559</v>
       </c>
       <c r="W5" t="n">
-        <v>-81.53989</v>
+        <v>-83.20277</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -958,10 +962,10 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
@@ -984,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1040,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.73856</v>
+        <v>46.30402</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.32056</v>
+        <v>-81.53989</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1230,35 +1234,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5.7</v>
+        <v>7.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>100</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>49.71016</v>
+        <v>44.73856</v>
       </c>
       <c r="W10" t="n">
-        <v>-94.40097</v>
+        <v>-76.32056</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1312,30 +1316,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.52895</v>
+        <v>46.23809</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.78169</v>
+        <v>-82.11991</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1394,30 +1398,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1439,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>48.69799</v>
+        <v>44.52895</v>
       </c>
       <c r="W12" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1476,35 +1480,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1521,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.5021</v>
+        <v>45.58868</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61301</v>
+        <v>-79.70944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1558,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1603,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1623,14 +1627,14 @@
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>45.58868</v>
+        <v>44.49976</v>
       </c>
       <c r="W14" t="n">
-        <v>-79.70944</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1640,30 +1644,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1685,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1696,23 +1700,269 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.49976</v>
+        <v>48.69799</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.61284999999999</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sultana</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MDI52E09NW00011</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Longbow Lake</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Gold, Molybdenum, Silver</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>100</v>
+      </c>
+      <c r="U16" t="n">
+        <v>43</v>
+      </c>
+      <c r="V16" t="n">
+        <v>49.71016</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-94.40097</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Dean and Williams</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MDI31C12SE00029</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Deloro</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Gold, Arsenic</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>13</v>
+      </c>
+      <c r="T17" t="n">
+        <v>325</v>
+      </c>
+      <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>44.5021</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-77.61301</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>13</v>
+      </c>
+      <c r="T18" t="n">
+        <v>325</v>
+      </c>
+      <c r="U18" t="n">
+        <v>42</v>
+      </c>
+      <c r="V18" t="n">
+        <v>48.24876</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-89.86754000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>46.30402</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -869,7 +865,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -988,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1040,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>46.30402</v>
+        <v>44.73856</v>
       </c>
       <c r="W7" t="n">
-        <v>-81.53989</v>
+        <v>-76.32056</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1066,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1115,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1135,14 +1131,14 @@
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1148,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1197,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1217,14 +1213,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1230,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1279,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="U10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>44.73856</v>
+        <v>46.23809</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.32056</v>
+        <v>-82.11991</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1316,30 +1312,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C12SE00024</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1361,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Gold, Copper</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>46.23809</v>
+        <v>44.5143</v>
       </c>
       <c r="W11" t="n">
-        <v>-82.11991</v>
+        <v>-77.61444</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
         </is>
       </c>
     </row>
@@ -1398,35 +1394,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1443,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.52895</v>
+        <v>45.58868</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.78169</v>
+        <v>-79.70944</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1480,35 +1476,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1525,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>45.58868</v>
+        <v>48.69799</v>
       </c>
       <c r="W13" t="n">
-        <v>-79.70944</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1558,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1576,7 +1572,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1585,7 +1581,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1607,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1614,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.49976</v>
+        <v>44.5021</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1640,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1685,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1696,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>48.69799</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1808,12 +1804,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1822,7 +1818,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1831,7 +1827,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1853,7 +1849,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,105 +1860,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>44.5021</v>
+        <v>44.49976</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.61301</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>13</v>
-      </c>
-      <c r="T18" t="n">
-        <v>325</v>
-      </c>
-      <c r="U18" t="n">
-        <v>42</v>
-      </c>
-      <c r="V18" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.5</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,10 +780,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -794,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>46.30402</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-81.53989</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -820,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -865,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -876,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W5" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -902,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -967,14 +971,14 @@
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.63956</v>
+        <v>46.30402</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.55477999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -984,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1040,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.73856</v>
+        <v>46.29559</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.32056</v>
+        <v>-83.20277</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1148,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1193,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1204,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.62168</v>
+        <v>44.73856</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.56963</v>
+        <v>-76.32056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1230,35 +1234,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.3</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>46.23809</v>
+        <v>44.62168</v>
       </c>
       <c r="W10" t="n">
-        <v>-82.11991</v>
+        <v>-76.56963</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1312,30 +1316,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.8</v>
+        <v>6.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Gold, Copper</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.5143</v>
+        <v>48.69799</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61444</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1394,35 +1398,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1439,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>45.58868</v>
+        <v>44.5021</v>
       </c>
       <c r="W12" t="n">
-        <v>-79.70944</v>
+        <v>-77.61301</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1476,30 +1480,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1521,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1541,14 +1545,14 @@
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>48.69799</v>
+        <v>44.49976</v>
       </c>
       <c r="W13" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1558,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1603,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.5021</v>
+        <v>45.58868</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61301</v>
+        <v>-79.70944</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1722,30 +1726,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.7</v>
+        <v>2.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1767,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Zinc, Copper</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,105 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V16" t="n">
-        <v>49.71016</v>
+        <v>48.24876</v>
       </c>
       <c r="W16" t="n">
-        <v>-94.40097</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Ackerman</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MDI31C05NE00018</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Deloro</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>12</v>
-      </c>
-      <c r="T17" t="n">
-        <v>300</v>
-      </c>
-      <c r="U17" t="n">
-        <v>43</v>
-      </c>
-      <c r="V17" t="n">
-        <v>44.49976</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-77.61284999999999</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -880,10 +880,10 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
@@ -1070,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1316,30 +1316,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1381,14 +1381,14 @@
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>48.69799</v>
+        <v>44.49976</v>
       </c>
       <c r="W11" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
@@ -1480,35 +1480,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.49976</v>
+        <v>45.58868</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61284999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1562,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>45.58868</v>
+        <v>44.52895</v>
       </c>
       <c r="W14" t="n">
-        <v>-79.70944</v>
+        <v>-77.78169</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1644,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>48.69799</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1726,30 +1726,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,21 +1782,267 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U16" t="n">
+        <v>43</v>
+      </c>
+      <c r="V16" t="n">
+        <v>49.71016</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-94.40097</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Massey</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MDI41J01NE00008</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Massey</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>12 drill hole(s) nearby · 1955–2005 · D Eldona Gold Mines Ltd, Donalda Mines Ltd · tested Copper</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>225</v>
+      </c>
+      <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>46.23809</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-82.11991</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cook</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI31C12SE00024</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deloro</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>225</v>
+      </c>
+      <c r="U18" t="n">
+        <v>43</v>
+      </c>
+      <c r="V18" t="n">
+        <v>44.5143</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-77.61444</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="n">
+        <v>300</v>
+      </c>
+      <c r="U19" t="n">
         <v>42</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V19" t="n">
         <v>48.24876</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W19" t="n">
         <v>-89.86754000000001</v>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -824,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -988,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W7" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1217,14 +1217,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1279,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U10" t="n">
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.62168</v>
+        <v>44.73856</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.56963</v>
+        <v>-76.32056</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
@@ -1618,10 +1618,10 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
@@ -1644,35 +1644,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>48.69799</v>
+        <v>49.71016</v>
       </c>
       <c r="W15" t="n">
-        <v>-93.27513999999999</v>
+        <v>-94.40097</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1726,35 +1726,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>49.71016</v>
+        <v>48.69799</v>
       </c>
       <c r="W16" t="n">
-        <v>-94.40097</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1808,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · D Eldona Gold Mines Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,185 +1864,21 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V17" t="n">
-        <v>46.23809</v>
+        <v>48.24876</v>
       </c>
       <c r="W17" t="n">
-        <v>-82.11991</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Cook</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI31C12SE00024</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Deloro</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>9</v>
-      </c>
-      <c r="T18" t="n">
-        <v>225</v>
-      </c>
-      <c r="U18" t="n">
-        <v>43</v>
-      </c>
-      <c r="V18" t="n">
-        <v>44.5143</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-77.61444</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>12</v>
-      </c>
-      <c r="T19" t="n">
-        <v>300</v>
-      </c>
-      <c r="U19" t="n">
-        <v>42</v>
-      </c>
-      <c r="V19" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X19" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -824,21 +824,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.29559</v>
+        <v>46.30402</v>
       </c>
       <c r="W5" t="n">
-        <v>-83.20277</v>
+        <v>-81.53989</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -906,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -988,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.62168</v>
+        <v>44.73856</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.56963</v>
+        <v>-76.32056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1279,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1316,17 +1316,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Jayfran-Pipawa</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31F04SE00036</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Vardy</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1334,24 +1334,24 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Nepheline Syenite, Uranium</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I11" t="b">
         <v>1</v>
       </c>
       <c r="J11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1984–1988 · Jayfran Enterprises Ltd, Pipawa Expl Ltd</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1370,25 +1370,29 @@
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
+        </is>
+      </c>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.49976</v>
+        <v>45.09484</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.76734999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
         </is>
       </c>
     </row>
@@ -1398,21 +1402,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1421,12 +1425,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1443,7 +1447,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1458,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.5021</v>
+        <v>49.71016</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61301</v>
+        <v>-94.40097</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1480,35 +1484,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1525,7 +1529,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1540,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>45.58868</v>
+        <v>44.5021</v>
       </c>
       <c r="W13" t="n">
-        <v>-79.70944</v>
+        <v>-77.61301</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1644,35 +1648,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1689,7 +1693,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1704,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>49.71016</v>
+        <v>48.69799</v>
       </c>
       <c r="W15" t="n">
-        <v>-94.40097</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1726,30 +1730,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1771,7 +1775,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1791,14 +1795,14 @@
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>48.69799</v>
+        <v>44.49976</v>
       </c>
       <c r="W16" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1808,35 +1812,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1853,7 +1857,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1870,15 +1874,97 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>45.58868</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-79.70944</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>13</v>
+      </c>
+      <c r="T18" t="n">
+        <v>325</v>
+      </c>
+      <c r="U18" t="n">
         <v>42</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V18" t="n">
         <v>48.24876</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W18" t="n">
         <v>-89.86754000000001</v>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -906,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T6" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -988,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W7" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1316,42 +1316,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jayfran-Pipawa</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31F04SE00036</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Vardy</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nepheline Syenite, Uranium</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
         <v>1</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1984–1988 · Jayfran Enterprises Ltd, Pipawa Expl Ltd</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1370,11 +1370,7 @@
       </c>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
-        </is>
-      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
         <v>9</v>
       </c>
@@ -1385,14 +1381,14 @@
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>45.09484</v>
+        <v>46.23809</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.76734999999999</v>
+        <v>-82.11991</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1402,35 +1398,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1447,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1458,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>49.71016</v>
+        <v>48.69799</v>
       </c>
       <c r="W12" t="n">
-        <v>-94.40097</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R L V Ekstrom, Unknown · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1566,21 +1562,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1611,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1622,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.52895</v>
+        <v>44.51686</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.78169</v>
+        <v>-77.62098</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1648,35 +1644,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1693,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1713,14 +1709,14 @@
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>48.69799</v>
+        <v>45.58868</v>
       </c>
       <c r="W15" t="n">
-        <v>-93.27513999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1730,21 +1726,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1775,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1786,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.49976</v>
+        <v>44.52895</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1812,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1857,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R L V Ekstrom, Unknown · tested Gold</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1868,23 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>45.58868</v>
+        <v>44.49976</v>
       </c>
       <c r="W17" t="n">
-        <v>-79.70944</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -824,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -889,14 +889,14 @@
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W5" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -906,21 +906,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.29559</v>
+        <v>46.30402</v>
       </c>
       <c r="W6" t="n">
-        <v>-83.20277</v>
+        <v>-81.53989</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -988,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1279,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.62168</v>
+        <v>44.73856</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.56963</v>
+        <v>-76.32056</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1398,30 +1398,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>48.69799</v>
+        <v>44.5021</v>
       </c>
       <c r="W12" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1480,21 +1480,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R L V Ekstrom, Unknown · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.5021</v>
+        <v>44.52895</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61301</v>
+        <v>-77.78169</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1562,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.51686</v>
+        <v>45.58868</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.62098</v>
+        <v>-79.70944</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1644,35 +1644,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1709,14 +1709,14 @@
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>45.58868</v>
+        <v>48.69799</v>
       </c>
       <c r="W15" t="n">
-        <v>-79.70944</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1726,21 +1726,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.52895</v>
+        <v>44.49976</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.78169</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1808,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R L V Ekstrom, Unknown · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,103 +1864,21 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V17" t="n">
-        <v>44.49976</v>
+        <v>48.24876</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.61284999999999</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>13</v>
-      </c>
-      <c r="T18" t="n">
-        <v>325</v>
-      </c>
-      <c r="U18" t="n">
-        <v>42</v>
-      </c>
-      <c r="V18" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X18" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -906,21 +906,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.30402</v>
+        <v>46.29559</v>
       </c>
       <c r="W6" t="n">
-        <v>-81.53989</v>
+        <v>-83.20277</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -988,21 +988,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>46.29559</v>
+        <v>46.30402</v>
       </c>
       <c r="W7" t="n">
-        <v>-83.20277</v>
+        <v>-81.53989</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1135,14 +1135,14 @@
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1217,14 +1217,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1316,30 +1316,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R L V Ekstrom, Unknown · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>46.23809</v>
+        <v>44.49976</v>
       </c>
       <c r="W11" t="n">
-        <v>-82.11991</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1398,30 +1398,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1463,14 +1463,14 @@
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.5021</v>
+        <v>48.69799</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61301</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1480,30 +1480,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.52895</v>
+        <v>46.23809</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.78169</v>
+        <v>-82.11991</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1562,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C12SE00024</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>45.58868</v>
+        <v>44.5143</v>
       </c>
       <c r="W14" t="n">
-        <v>-79.70944</v>
+        <v>-77.61444</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1644,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>48.69799</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1726,21 +1726,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1749,12 +1749,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.49976</v>
+        <v>49.71016</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61284999999999</v>
+        <v>-94.40097</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1808,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1870,15 +1870,179 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>45.58868</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-79.70944</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dean and Williams</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI31C12SE00029</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deloro</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gold, Arsenic</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6 drill hole(s) nearby · 1960–1985 · R L V Ekstrom, Unknown · tested Gold</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>13</v>
+      </c>
+      <c r="T18" t="n">
+        <v>325</v>
+      </c>
+      <c r="U18" t="n">
+        <v>43</v>
+      </c>
+      <c r="V18" t="n">
+        <v>44.5021</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-77.61301</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="n">
+        <v>300</v>
+      </c>
+      <c r="U19" t="n">
         <v>42</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V19" t="n">
         <v>48.24876</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W19" t="n">
         <v>-89.86754000000001</v>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
         <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -824,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -906,21 +906,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.29559</v>
+        <v>46.30402</v>
       </c>
       <c r="W6" t="n">
-        <v>-83.20277</v>
+        <v>-81.53989</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -988,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W7" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1135,14 +1135,14 @@
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1217,14 +1217,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1290,10 +1290,10 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="U10" t="n">
         <v>46</v>
@@ -1316,35 +1316,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R L V Ekstrom, Unknown · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1381,14 +1381,14 @@
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.49976</v>
+        <v>45.58868</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61284999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1398,30 +1398,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1463,14 +1463,14 @@
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>48.69799</v>
+        <v>44.49976</v>
       </c>
       <c r="W12" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1576,7 +1576,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.5143</v>
+        <v>44.5021</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61444</v>
+        <v>-77.61301</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1700,10 +1700,10 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1808,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,23 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>45.58868</v>
+        <v>44.51686</v>
       </c>
       <c r="W17" t="n">
-        <v>-79.70944</v>
+        <v>-77.62098</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1890,30 +1890,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1935,7 +1935,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R L V Ekstrom, Unknown · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1946,23 +1946,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U18" t="n">
         <v>43</v>
       </c>
       <c r="V18" t="n">
-        <v>44.5021</v>
+        <v>48.69799</v>
       </c>
       <c r="W18" t="n">
-        <v>-77.61301</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>46.30402</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -824,30 +820,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +865,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +876,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W5" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -906,21 +902,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -929,7 +925,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.30402</v>
+        <v>46.29559</v>
       </c>
       <c r="W6" t="n">
-        <v>-81.53989</v>
+        <v>-83.20277</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -988,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1040,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>44.63956</v>
+        <v>44.62168</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.56963</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1066,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,7 +1089,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1122,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.62168</v>
+        <v>44.73856</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.56963</v>
+        <v>-76.32056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1234,30 +1230,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.7</v>
+        <v>0.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1279,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>44.73856</v>
+        <v>45.58868</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.32056</v>
+        <v>-79.70944</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1316,35 +1312,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>45.58868</v>
+        <v>49.71016</v>
       </c>
       <c r="W11" t="n">
-        <v>-79.70944</v>
+        <v>-94.40097</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1398,30 +1394,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1463,14 +1459,14 @@
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.49976</v>
+        <v>48.69799</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61284999999999</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1480,30 +1476,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>46.23809</v>
+        <v>44.49976</v>
       </c>
       <c r="W13" t="n">
-        <v>-82.11991</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1726,35 +1722,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,269 +1778,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>49.71016</v>
+        <v>46.23809</v>
       </c>
       <c r="W16" t="n">
-        <v>-94.40097</v>
+        <v>-82.11991</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Hawk Eye</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MDI31C12SE00032</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Deloro</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>8</v>
-      </c>
-      <c r="T17" t="n">
-        <v>200</v>
-      </c>
-      <c r="U17" t="n">
-        <v>43</v>
-      </c>
-      <c r="V17" t="n">
-        <v>44.51686</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-77.62098</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Reef Point Occurrence</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI52C11NW00007</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Windy Point</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Copper, Nickel</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>12</v>
-      </c>
-      <c r="T18" t="n">
-        <v>300</v>
-      </c>
-      <c r="U18" t="n">
-        <v>43</v>
-      </c>
-      <c r="V18" t="n">
-        <v>48.69799</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-93.27513999999999</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>12</v>
-      </c>
-      <c r="T19" t="n">
-        <v>300</v>
-      </c>
-      <c r="U19" t="n">
-        <v>42</v>
-      </c>
-      <c r="V19" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -783,7 +783,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -876,10 +876,10 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
@@ -947,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -984,21 +984,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1040,23 +1040,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U7" t="n">
         <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>44.62168</v>
+        <v>44.73856</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.56963</v>
+        <v>-76.32056</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1066,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1111,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1122,23 +1122,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1148,21 +1148,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1213,14 +1213,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1230,35 +1230,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1275,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U10" t="n">
         <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>45.58868</v>
+        <v>48.69799</v>
       </c>
       <c r="W10" t="n">
-        <v>-79.70944</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1312,21 +1312,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1357,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T11" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>49.71016</v>
+        <v>44.49976</v>
       </c>
       <c r="W11" t="n">
-        <v>-94.40097</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1394,30 +1394,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1439,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1459,14 +1459,14 @@
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>48.69799</v>
+        <v>44.5021</v>
       </c>
       <c r="W12" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1476,21 +1476,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1521,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.49976</v>
+        <v>49.71016</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61284999999999</v>
+        <v>-94.40097</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1558,35 +1558,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1603,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1614,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.5021</v>
+        <v>45.58868</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61301</v>
+        <v>-79.70944</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1722,35 +1722,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1767,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,23 +1778,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V16" t="n">
-        <v>46.23809</v>
+        <v>48.24876</v>
       </c>
       <c r="W16" t="n">
-        <v>-82.11991</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,30 +738,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -783,7 +783,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -794,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U4" t="n">
         <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W4" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -820,30 +820,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -865,7 +865,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -876,23 +876,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>44.63956</v>
+        <v>46.30402</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.55477999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -984,21 +984,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1040,23 +1040,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1148,21 +1148,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1193,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1204,23 +1204,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.62168</v>
+        <v>44.73856</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.56963</v>
+        <v>-76.32056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1230,35 +1230,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1275,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
         <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>48.69799</v>
+        <v>45.58868</v>
       </c>
       <c r="W10" t="n">
-        <v>-93.27513999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1312,30 +1312,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1357,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1377,14 +1377,14 @@
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.49976</v>
+        <v>48.69799</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61284999999999</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1394,21 +1394,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1439,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.5021</v>
+        <v>49.71016</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61301</v>
+        <v>-94.40097</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1476,21 +1476,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1521,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>49.71016</v>
+        <v>44.52895</v>
       </c>
       <c r="W13" t="n">
-        <v>-94.40097</v>
+        <v>-77.78169</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1558,35 +1558,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1603,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1614,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>45.58868</v>
+        <v>44.49976</v>
       </c>
       <c r="W14" t="n">
-        <v>-79.70944</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1640,30 +1640,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1685,7 +1685,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · D Eldona Gold Mines Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1696,23 +1696,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>46.23809</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-82.11991</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1722,35 +1722,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.8</v>
+        <v>1.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1767,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1784,15 +1784,97 @@
         <v>300</v>
       </c>
       <c r="U16" t="n">
+        <v>43</v>
+      </c>
+      <c r="V16" t="n">
+        <v>44.5021</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-77.61301</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T17" t="n">
+        <v>300</v>
+      </c>
+      <c r="U17" t="n">
         <v>42</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V17" t="n">
         <v>48.24876</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W17" t="n">
         <v>-89.86754000000001</v>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,30 +738,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -783,7 +783,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -794,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U4" t="n">
         <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -902,30 +902,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -984,21 +984,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1049,14 +1049,14 @@
         <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1066,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1131,14 +1131,14 @@
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1312,30 +1312,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1357,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1377,14 +1377,14 @@
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>48.69799</v>
+        <v>44.5021</v>
       </c>
       <c r="W11" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1476,30 +1476,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1521,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.52895</v>
+        <v>48.69799</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.78169</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1722,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1767,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,105 +1778,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.5021</v>
+        <v>44.52895</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61301</v>
+        <v>-77.78169</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>12</v>
-      </c>
-      <c r="T17" t="n">
-        <v>300</v>
-      </c>
-      <c r="U17" t="n">
-        <v>42</v>
-      </c>
-      <c r="V17" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,30 +738,30 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -783,7 +783,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -794,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T4" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U4" t="n">
         <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -902,30 +902,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -984,21 +984,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1049,14 +1049,14 @@
         <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1066,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1131,14 +1131,14 @@
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1312,30 +1312,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1357,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1377,14 +1377,14 @@
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.5021</v>
+        <v>48.69799</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61301</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1476,30 +1476,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1521,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>48.69799</v>
+        <v>44.52895</v>
       </c>
       <c r="W13" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1722,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1767,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,23 +1778,105 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.52895</v>
+        <v>44.5021</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.78169</v>
+        <v>-77.61301</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T17" t="n">
+        <v>300</v>
+      </c>
+      <c r="U17" t="n">
+        <v>42</v>
+      </c>
+      <c r="V17" t="n">
+        <v>48.24876</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-89.86754000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,35 +738,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,10 +780,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -794,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>44.63956</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -902,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -984,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1040,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.62168</v>
+        <v>46.29559</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.56963</v>
+        <v>-83.20277</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1111,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1122,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1148,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1193,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1204,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1230,30 +1234,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1292,17 +1296,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>45.58868</v>
+        <v>44.62168</v>
       </c>
       <c r="W10" t="n">
-        <v>-79.70944</v>
+        <v>-76.56963</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1312,35 +1316,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>48.69799</v>
+        <v>45.58868</v>
       </c>
       <c r="W11" t="n">
-        <v>-93.27513999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1394,21 +1398,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1417,12 +1421,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1439,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>49.71016</v>
+        <v>44.49976</v>
       </c>
       <c r="W12" t="n">
-        <v>-94.40097</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1476,21 +1480,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1499,7 +1503,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1521,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.52895</v>
+        <v>44.5021</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.78169</v>
+        <v>-77.61301</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1558,30 +1562,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1603,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.49976</v>
+        <v>46.23809</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61284999999999</v>
+        <v>-82.11991</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1640,21 +1644,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1663,7 +1667,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1685,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · D Eldona Gold Mines Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1696,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>46.23809</v>
+        <v>48.69799</v>
       </c>
       <c r="W15" t="n">
-        <v>-82.11991</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1726,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1736,7 +1740,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1745,7 +1749,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1767,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.5021</v>
+        <v>44.51686</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61301</v>
+        <v>-77.62098</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1804,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1849,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1860,21 +1864,103 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>44.52895</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-77.78169</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>13</v>
+      </c>
+      <c r="T18" t="n">
+        <v>325</v>
+      </c>
+      <c r="U18" t="n">
         <v>42</v>
       </c>
-      <c r="V17" t="n">
+      <c r="V18" t="n">
         <v>48.24876</v>
       </c>
-      <c r="W17" t="n">
+      <c r="W18" t="n">
         <v>-89.86754000000001</v>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -738,35 +738,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>44.63956</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -906,30 +902,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -988,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.9</v>
+        <v>0.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1040,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>46.29559</v>
+        <v>44.62168</v>
       </c>
       <c r="W7" t="n">
-        <v>-83.20277</v>
+        <v>-76.56963</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1066,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,7 +1089,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1122,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1148,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1171,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1204,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1234,30 +1230,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1279,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1296,17 +1292,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>44.62168</v>
+        <v>45.58868</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.56963</v>
+        <v>-79.70944</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1316,35 +1312,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>45.58868</v>
+        <v>44.52895</v>
       </c>
       <c r="W11" t="n">
-        <v>-79.70944</v>
+        <v>-77.78169</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1398,30 +1394,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.49976</v>
+        <v>46.23809</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61284999999999</v>
+        <v>-82.11991</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1476,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C12SE00024</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1494,7 +1490,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1503,7 +1499,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.5021</v>
+        <v>44.5143</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61301</v>
+        <v>-77.61444</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
         </is>
       </c>
     </row>
@@ -1562,30 +1558,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1607,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1614,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>46.23809</v>
+        <v>44.5021</v>
       </c>
       <c r="W14" t="n">
-        <v>-82.11991</v>
+        <v>-77.61301</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1644,35 +1640,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1689,7 +1685,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1696,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>48.69799</v>
+        <v>49.71016</v>
       </c>
       <c r="W15" t="n">
-        <v>-93.27513999999999</v>
+        <v>-94.40097</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1722,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1740,7 +1736,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1771,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1778,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.51686</v>
+        <v>44.49976</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.62098</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1808,30 +1804,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1853,7 +1849,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,23 +1860,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>44.52895</v>
+        <v>48.69799</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.78169</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1946,10 +1942,10 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U18" t="n">
         <v>42</v>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -738,35 +738,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,10 +780,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -794,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>44.63956</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -902,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -984,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1040,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.62168</v>
+        <v>46.29559</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.56963</v>
+        <v>-83.20277</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1089,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1111,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1122,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1148,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1193,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1204,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1230,30 +1234,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1292,17 +1296,17 @@
         <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>45.58868</v>
+        <v>44.62168</v>
       </c>
       <c r="W10" t="n">
-        <v>-79.70944</v>
+        <v>-76.56963</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1312,35 +1316,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.52895</v>
+        <v>45.58868</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.78169</v>
+        <v>-79.70944</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1394,30 +1398,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.3</v>
+        <v>1.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1439,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>46.23809</v>
+        <v>44.49976</v>
       </c>
       <c r="W12" t="n">
-        <v>-82.11991</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1480,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1490,7 +1494,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8</v>
+        <v>1.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1499,7 +1503,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1521,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.5143</v>
+        <v>44.5021</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61444</v>
+        <v>-77.61301</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1558,30 +1562,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1603,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.5021</v>
+        <v>46.23809</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61301</v>
+        <v>-82.11991</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1640,35 +1644,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1685,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1696,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>49.71016</v>
+        <v>48.69799</v>
       </c>
       <c r="W15" t="n">
-        <v>-94.40097</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1726,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1736,7 +1740,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1767,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.49976</v>
+        <v>44.51686</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.62098</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1804,30 +1808,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1849,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1860,23 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>48.69799</v>
+        <v>44.52895</v>
       </c>
       <c r="W17" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1942,10 +1946,10 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
         <v>42</v>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -738,35 +738,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,10 +780,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Au 1120g/t, Cu 0.66%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -800,17 +804,17 @@
         <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>44.63956</v>
+        <v>44.55039</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.55477999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -902,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -984,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1040,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.62168</v>
+        <v>46.29559</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.56963</v>
+        <v>-83.20277</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1148,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1193,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1204,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1230,30 +1234,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9</v>
+        <v>7.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>45.58868</v>
+        <v>44.73856</v>
       </c>
       <c r="W10" t="n">
-        <v>-79.70944</v>
+        <v>-76.32056</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1312,21 +1316,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1335,7 +1339,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.52895</v>
+        <v>44.5021</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.78169</v>
+        <v>-77.61301</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1394,35 +1398,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1439,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>46.23809</v>
+        <v>49.71016</v>
       </c>
       <c r="W12" t="n">
-        <v>-82.11991</v>
+        <v>-94.40097</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1480,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1490,7 +1494,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1521,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.5143</v>
+        <v>44.51686</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61444</v>
+        <v>-77.62098</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1558,21 +1562,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1581,7 +1585,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1603,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.5021</v>
+        <v>44.52895</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61301</v>
+        <v>-77.78169</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1640,35 +1644,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1685,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1696,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>49.71016</v>
+        <v>48.69799</v>
       </c>
       <c r="W15" t="n">
-        <v>-94.40097</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,10 +1782,10 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
@@ -1804,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1849,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1860,23 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>48.69799</v>
+        <v>45.58868</v>
       </c>
       <c r="W17" t="n">
-        <v>-93.27513999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1886,35 +1890,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1931,7 +1935,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1942,21 +1946,103 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T18" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U18" t="n">
+        <v>43</v>
+      </c>
+      <c r="V18" t="n">
+        <v>46.23809</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-82.11991</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>13</v>
+      </c>
+      <c r="T19" t="n">
+        <v>325</v>
+      </c>
+      <c r="U19" t="n">
         <v>42</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V19" t="n">
         <v>48.24876</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W19" t="n">
         <v>-89.86754000000001</v>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
         <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>275</v>
+        <v>200</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
@@ -1290,10 +1290,10 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
         <v>46</v>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.5021</v>
+        <v>44.51686</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61301</v>
+        <v>-77.62098</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1398,35 +1398,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>49.71016</v>
+        <v>48.69799</v>
       </c>
       <c r="W12" t="n">
-        <v>-94.40097</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1480,35 +1480,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.51686</v>
+        <v>45.58868</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.62098</v>
+        <v>-79.70944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1562,21 +1562,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.52895</v>
+        <v>44.49976</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.78169</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1644,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>48.69799</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1740,7 +1740,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1791,14 +1791,14 @@
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.49976</v>
+        <v>44.5021</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1808,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · D Eldona Gold Mines Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,187 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>45.58868</v>
+        <v>46.23809</v>
       </c>
       <c r="W17" t="n">
-        <v>-79.70944</v>
+        <v>-82.11991</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Massey</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI41J01NE00008</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Massey</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>9</v>
-      </c>
-      <c r="T18" t="n">
-        <v>225</v>
-      </c>
-      <c r="U18" t="n">
-        <v>43</v>
-      </c>
-      <c r="V18" t="n">
-        <v>46.23809</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-82.11991</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>13</v>
-      </c>
-      <c r="T19" t="n">
-        <v>325</v>
-      </c>
-      <c r="U19" t="n">
-        <v>42</v>
-      </c>
-      <c r="V19" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,35 +738,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>44.63956</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -906,30 +902,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -988,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1040,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>46.29559</v>
+        <v>44.55883</v>
       </c>
       <c r="W7" t="n">
-        <v>-83.20277</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1066,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1115,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1135,14 +1131,14 @@
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1148,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1171,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1204,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.62168</v>
+        <v>44.73856</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.56963</v>
+        <v>-76.32056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1230,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1279,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="U10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>44.73856</v>
+        <v>44.5021</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.32056</v>
+        <v>-77.61301</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1316,21 +1312,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1361,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.51686</v>
+        <v>44.52895</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.62098</v>
+        <v>-77.78169</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1398,30 +1394,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>48.69799</v>
+        <v>44.49976</v>
       </c>
       <c r="W12" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1562,30 +1558,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.6</v>
+        <v>6.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1607,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1614,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.49976</v>
+        <v>48.69799</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61284999999999</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1640,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1685,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1709,14 +1705,14 @@
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>46.23809</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-82.11991</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1726,21 +1722,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1749,12 +1745,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,105 +1778,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.5021</v>
+        <v>49.71016</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61301</v>
+        <v>-94.40097</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Massey</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MDI41J01NE00008</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Massey</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Copper</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Copper, Gold, Silver</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · D Eldona Gold Mines Ltd, Donalda Mines Ltd · tested Copper</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>225</v>
-      </c>
-      <c r="U17" t="n">
-        <v>43</v>
-      </c>
-      <c r="V17" t="n">
-        <v>46.23809</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-82.11991</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,35 +738,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,10 +780,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Cu 3.50%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -794,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>44.63956</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -865,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -902,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -984,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1040,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>200</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.55883</v>
+        <v>46.29559</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.57349000000001</v>
+        <v>-83.20277</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1111,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1131,14 +1135,14 @@
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1148,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1193,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1204,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1230,35 +1234,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.5021</v>
+        <v>44.73856</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.61301</v>
+        <v>-76.32056</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1312,35 +1316,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.52895</v>
+        <v>45.58868</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.78169</v>
+        <v>-79.70944</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1398,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1408,7 +1412,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1439,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.49976</v>
+        <v>44.51686</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.62098</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1476,35 +1480,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1521,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1541,14 +1545,14 @@
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>45.58868</v>
+        <v>48.69799</v>
       </c>
       <c r="W13" t="n">
-        <v>-79.70944</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1558,21 +1562,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1581,7 +1585,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1603,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>48.69799</v>
+        <v>46.23809</v>
       </c>
       <c r="W14" t="n">
-        <v>-93.27513999999999</v>
+        <v>-82.11991</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1640,35 +1644,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1685,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1696,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>100</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>46.23809</v>
+        <v>49.71016</v>
       </c>
       <c r="W15" t="n">
-        <v>-82.11991</v>
+        <v>-94.40097</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1722,21 +1726,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.7</v>
+        <v>1.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1745,12 +1749,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1767,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,23 +1782,187 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>49.71016</v>
+        <v>44.5021</v>
       </c>
       <c r="W16" t="n">
-        <v>-94.40097</v>
+        <v>-77.61301</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Ledyard</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MDI31C12SW00008</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Cordova Mines</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>225</v>
+      </c>
+      <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>44.52895</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-77.78169</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ackerman</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI31C05NE00018</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deloro</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>13</v>
+      </c>
+      <c r="T18" t="n">
+        <v>325</v>
+      </c>
+      <c r="U18" t="n">
+        <v>43</v>
+      </c>
+      <c r="V18" t="n">
+        <v>44.49976</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-77.61284999999999</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -824,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W5" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -906,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -971,14 +971,14 @@
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.63956</v>
+        <v>46.30402</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.55477999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,10 +1044,10 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>200</v>
+        <v>275</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
@@ -1070,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1217,14 +1217,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1279,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1316,35 +1316,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9</v>
+        <v>4.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>45.58868</v>
+        <v>46.23809</v>
       </c>
       <c r="W11" t="n">
-        <v>-79.70944</v>
+        <v>-82.11991</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.51686</v>
+        <v>44.49976</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.62098</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1480,30 +1480,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>48.69799</v>
+        <v>44.5021</v>
       </c>
       <c r="W13" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1562,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.3</v>
+        <v>0.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>46.23809</v>
+        <v>45.58868</v>
       </c>
       <c r="W14" t="n">
-        <v>-82.11991</v>
+        <v>-79.70944</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1644,21 +1644,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>49.71016</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-94.40097</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1726,30 +1726,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1791,14 +1791,14 @@
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.5021</v>
+        <v>48.69799</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61301</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1808,21 +1808,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Sudbury Contact Mines Ltd, Goldbrook Expl Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,23 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>44.52895</v>
+        <v>44.51686</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.78169</v>
+        <v>-77.62098</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1890,35 +1890,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1935,7 +1935,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1952,17 +1952,17 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V18" t="n">
-        <v>44.49976</v>
+        <v>48.24876</v>
       </c>
       <c r="W18" t="n">
-        <v>-77.61284999999999</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -824,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T5" t="n">
-        <v>300</v>
+        <v>275</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -988,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>275</v>
+        <v>300</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W7" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1316,30 +1316,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>46.23809</v>
+        <v>44.52895</v>
       </c>
       <c r="W11" t="n">
-        <v>-82.11991</v>
+        <v>-77.78169</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1562,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>45.58868</v>
+        <v>48.69799</v>
       </c>
       <c r="W14" t="n">
-        <v>-79.70944</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1644,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>46.23809</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-82.11991</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1726,35 +1726,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>48.69799</v>
+        <v>49.71016</v>
       </c>
       <c r="W16" t="n">
-        <v>-93.27513999999999</v>
+        <v>-94.40097</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1808,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Sudbury Contact Mines Ltd, Goldbrook Expl Ltd</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,23 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>44.51686</v>
+        <v>45.58868</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.62098</v>
+        <v>-79.70944</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1946,10 +1946,10 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U18" t="n">
         <v>42</v>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
         <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Zinc, Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1217,14 +1217,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1299,14 +1299,14 @@
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1316,30 +1316,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.52895</v>
+        <v>48.69799</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.78169</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1480,21 +1480,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.5021</v>
+        <v>44.52895</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61301</v>
+        <v>-77.78169</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1562,30 +1562,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.5</v>
+        <v>1.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1627,14 +1627,14 @@
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>48.69799</v>
+        <v>44.5021</v>
       </c>
       <c r="W14" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · D Eldona Gold Mines Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1726,35 +1726,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.7</v>
+        <v>0.9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>49.71016</v>
+        <v>45.58868</v>
       </c>
       <c r="W16" t="n">
-        <v>-94.40097</v>
+        <v>-79.70944</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1808,35 +1808,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9</v>
+        <v>2.8</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1870,97 +1870,15 @@
         <v>325</v>
       </c>
       <c r="U17" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V17" t="n">
-        <v>45.58868</v>
+        <v>48.24876</v>
       </c>
       <c r="W17" t="n">
-        <v>-79.70944</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>12</v>
-      </c>
-      <c r="T18" t="n">
-        <v>300</v>
-      </c>
-      <c r="U18" t="n">
-        <v>42</v>
-      </c>
-      <c r="V18" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X18" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X17"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="U4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>46.29559</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -824,21 +820,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -847,7 +843,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +865,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +876,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.29559</v>
+        <v>46.30402</v>
       </c>
       <c r="W5" t="n">
-        <v>-83.20277</v>
+        <v>-81.53989</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -906,30 +902,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -988,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1040,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>44.63956</v>
+        <v>44.55883</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1066,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,7 +1089,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1122,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1148,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>7.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1171,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1204,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.62168</v>
+        <v>44.73856</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.56963</v>
+        <v>-76.32056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1234,35 +1230,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1279,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>44.55883</v>
+        <v>44.52895</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.57349000000001</v>
+        <v>-77.78169</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1316,30 +1312,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1361,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>48.69799</v>
+        <v>44.49976</v>
       </c>
       <c r="W11" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1398,35 +1394,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1443,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.49976</v>
+        <v>45.58868</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61284999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1480,21 +1476,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1503,7 +1499,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1525,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.52895</v>
+        <v>44.5021</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.78169</v>
+        <v>-77.61301</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1562,21 +1558,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1585,12 +1581,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1607,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1614,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.5021</v>
+        <v>49.71016</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61301</v>
+        <v>-94.40097</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1685,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · D Eldona Gold Mines Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1726,35 +1722,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9</v>
+        <v>6.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,105 +1778,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>45.58868</v>
+        <v>48.69799</v>
       </c>
       <c r="W16" t="n">
-        <v>-79.70944</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>13</v>
-      </c>
-      <c r="T17" t="n">
-        <v>325</v>
-      </c>
-      <c r="U17" t="n">
-        <v>42</v>
-      </c>
-      <c r="V17" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,10 +780,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Au 1120g/t, Cu 0.66%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -794,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>46.29559</v>
+        <v>44.55039</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20277</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -820,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -865,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -885,14 +889,14 @@
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W5" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -902,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -984,17 +988,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1002,12 +1006,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1046,17 +1050,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.55883</v>
+        <v>46.30402</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.57349000000001</v>
+        <v>-81.53989</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1148,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1193,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1204,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1230,35 +1234,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.52895</v>
+        <v>44.73856</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.78169</v>
+        <v>-76.32056</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1312,30 +1316,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.49976</v>
+        <v>46.23809</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61284999999999</v>
+        <v>-82.11991</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1476,12 +1480,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1490,7 +1494,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1499,7 +1503,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1521,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.5021</v>
+        <v>44.49976</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61301</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1640,30 +1644,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1685,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1705,14 +1709,14 @@
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>46.23809</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-82.11991</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1722,30 +1726,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6.5</v>
+        <v>0.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1767,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1778,23 +1782,269 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
+        <v>44.51686</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-77.62098</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Reef Point Occurrence</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MDI52C11NW00007</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Windy Point</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T17" t="n">
+        <v>300</v>
+      </c>
+      <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
         <v>48.69799</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W17" t="n">
         <v>-93.27513999999999</v>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Dean and Williams</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI31C12SE00029</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deloro</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Gold, Arsenic</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>13</v>
+      </c>
+      <c r="T18" t="n">
+        <v>325</v>
+      </c>
+      <c r="U18" t="n">
+        <v>43</v>
+      </c>
+      <c r="V18" t="n">
+        <v>44.5021</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-77.61301</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="n">
+        <v>300</v>
+      </c>
+      <c r="U19" t="n">
+        <v>42</v>
+      </c>
+      <c r="V19" t="n">
+        <v>48.24876</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-89.86754000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -824,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Crownbridge</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06NE00046</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Kynoch</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>18.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -866,10 +866,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Cu 2.01%</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>To a depth of 1000 feet, total reserves, including 10 % allowance for dilution, are stated to be 415 000 tons, grading 1.8% Cu, over an average width of 6.5 feet (Northern Miner, May 27, 1965).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +884,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V5" t="n">
-        <v>44.63956</v>
+        <v>46.4923</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.03964000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00046</t>
         </is>
       </c>
     </row>
@@ -906,30 +910,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +955,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +966,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -988,21 +992,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>1.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1011,7 +1015,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1048,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>46.30402</v>
+        <v>46.29559</v>
       </c>
       <c r="W7" t="n">
-        <v>-81.53989</v>
+        <v>-83.20277</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1070,30 +1074,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1119,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1132,17 +1136,17 @@
         <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V8" t="n">
-        <v>44.62168</v>
+        <v>46.30402</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.56963</v>
+        <v>-81.53989</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1156,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1197,7 +1201,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1217,14 +1221,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1238,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.7</v>
+        <v>4.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1257,7 +1261,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1279,7 +1283,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1294,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.73856</v>
+        <v>44.55883</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.32056</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1316,35 +1320,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.3</v>
+        <v>7.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1365,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1376,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V11" t="n">
-        <v>46.23809</v>
+        <v>44.73856</v>
       </c>
       <c r="W11" t="n">
-        <v>-82.11991</v>
+        <v>-76.32056</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1480,21 +1484,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1525,7 +1529,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1540,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.49976</v>
+        <v>44.52895</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1562,35 +1566,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1607,7 +1611,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1622,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>49.71016</v>
+        <v>46.23809</v>
       </c>
       <c r="W14" t="n">
-        <v>-94.40097</v>
+        <v>-82.11991</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1648,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1693,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1704,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>48.69799</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1730,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1740,7 +1744,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1749,7 +1753,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1771,7 +1775,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1786,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.51686</v>
+        <v>44.5021</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.62098</v>
+        <v>-77.61301</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1808,35 +1812,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1853,7 +1857,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,23 +1868,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>48.69799</v>
+        <v>49.71016</v>
       </c>
       <c r="W17" t="n">
-        <v>-93.27513999999999</v>
+        <v>-94.40097</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1890,12 +1894,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1904,7 +1908,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1913,7 +1917,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1935,7 +1939,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1946,23 +1950,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T18" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U18" t="n">
         <v>43</v>
       </c>
       <c r="V18" t="n">
-        <v>44.5021</v>
+        <v>44.49976</v>
       </c>
       <c r="W18" t="n">
-        <v>-77.61301</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -910,30 +910,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -955,7 +955,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -966,23 +966,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.63956</v>
+        <v>46.30402</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.55477999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1074,30 +1074,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1119,7 +1119,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1130,23 +1130,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U8" t="n">
         <v>48</v>
       </c>
       <c r="V8" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W8" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1156,21 +1156,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1221,14 +1221,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1238,21 +1238,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1283,7 +1283,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1294,23 +1294,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U10" t="n">
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1320,21 +1320,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1365,7 +1365,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1376,23 +1376,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>46</v>
       </c>
       <c r="V11" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1402,35 +1402,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1447,7 +1447,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1458,23 +1458,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>45.58868</v>
+        <v>49.71016</v>
       </c>
       <c r="W12" t="n">
-        <v>-79.70944</v>
+        <v>-94.40097</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1484,35 +1484,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1529,7 +1529,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1540,23 +1540,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.52895</v>
+        <v>45.58868</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.78169</v>
+        <v>-79.70944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1566,30 +1566,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1611,7 +1611,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1622,23 +1622,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>46.23809</v>
+        <v>44.5021</v>
       </c>
       <c r="W14" t="n">
-        <v>-82.11991</v>
+        <v>-77.61301</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1704,10 +1704,10 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1775,7 +1775,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1795,14 +1795,14 @@
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.5021</v>
+        <v>44.49976</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61301</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1812,42 +1812,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Jayfran-Pipawa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31F04SE00036</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Vardy</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Nepheline Syenite, Uranium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I17" t="b">
         <v>1</v>
       </c>
       <c r="J17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>7 drill hole(s) nearby · 1984–1988 · Jayfran Enterprises Ltd, Pipawa Expl Ltd</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1866,25 +1866,29 @@
       </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
+        </is>
+      </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>49.71016</v>
+        <v>45.09484</v>
       </c>
       <c r="W17" t="n">
-        <v>-94.40097</v>
+        <v>-77.76734999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
         </is>
       </c>
     </row>
@@ -1894,21 +1898,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1939,7 +1943,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1950,23 +1954,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="U18" t="n">
         <v>43</v>
       </c>
       <c r="V18" t="n">
-        <v>44.49976</v>
+        <v>44.52895</v>
       </c>
       <c r="W18" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -2032,10 +2036,10 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T19" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U19" t="n">
         <v>42</v>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -738,35 +738,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -804,17 +800,17 @@
         <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>44.55039</v>
+        <v>44.63956</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.36235000000001</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -824,21 +820,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Crownbridge</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41J06NE00046</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kynoch</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18.8</v>
+        <v>1.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -847,7 +843,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -866,14 +862,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Cu 2.01%</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>To a depth of 1000 feet, total reserves, including 10 % allowance for dilution, are stated to be 415 000 tons, grading 1.8% Cu, over an average width of 6.5 feet (Northern Miner, May 27, 1965).</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -884,23 +876,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="U5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.4923</v>
+        <v>46.29559</v>
       </c>
       <c r="W5" t="n">
-        <v>-83.03964000000001</v>
+        <v>-83.20277</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00046</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -992,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.9</v>
+        <v>7.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1037,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1054,17 +1046,17 @@
         <v>275</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>46.29559</v>
+        <v>44.73856</v>
       </c>
       <c r="W7" t="n">
-        <v>-83.20277</v>
+        <v>-76.32056</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1074,30 +1066,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1119,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1130,23 +1122,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T8" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.63956</v>
+        <v>44.55883</v>
       </c>
       <c r="W8" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1156,21 +1148,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1201,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1221,14 +1213,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1238,35 +1230,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.7</v>
+        <v>1.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1283,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1294,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T10" t="n">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="U10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>44.73856</v>
+        <v>44.52895</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.32056</v>
+        <v>-77.78169</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1320,35 +1312,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1365,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1382,17 +1374,17 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.62168</v>
+        <v>44.5021</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.56963</v>
+        <v>-77.61301</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1402,35 +1394,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.7</v>
+        <v>4.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1447,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1458,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>49.71016</v>
+        <v>46.23809</v>
       </c>
       <c r="W12" t="n">
-        <v>-94.40097</v>
+        <v>-82.11991</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1566,30 +1558,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.3</v>
+        <v>6.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1611,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1622,23 +1614,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.5021</v>
+        <v>48.69799</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61301</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1648,30 +1640,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1693,7 +1685,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1713,346 +1705,14 @@
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>48.69799</v>
+        <v>44.49976</v>
       </c>
       <c r="W15" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Ackerman</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>MDI31C05NE00018</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Deloro</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, Belmar Resc Inc · tested Gold</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
-        <v>12</v>
-      </c>
-      <c r="T16" t="n">
-        <v>300</v>
-      </c>
-      <c r="U16" t="n">
-        <v>43</v>
-      </c>
-      <c r="V16" t="n">
-        <v>44.49976</v>
-      </c>
-      <c r="W16" t="n">
-        <v>-77.61284999999999</v>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Jayfran-Pipawa</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MDI31F04SE00036</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Vardy</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Other metallic</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Nepheline Syenite, Uranium</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Deposit</t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>1</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>7 drill hole(s) nearby · 1984–1988 · Jayfran Enterprises Ltd, Pipawa Expl Ltd</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
-        </is>
-      </c>
-      <c r="S17" t="n">
-        <v>9</v>
-      </c>
-      <c r="T17" t="n">
-        <v>225</v>
-      </c>
-      <c r="U17" t="n">
-        <v>43</v>
-      </c>
-      <c r="V17" t="n">
-        <v>45.09484</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-77.76734999999999</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Ledyard</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI31C12SW00008</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Cordova Mines</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>10</v>
-      </c>
-      <c r="T18" t="n">
-        <v>250</v>
-      </c>
-      <c r="U18" t="n">
-        <v>43</v>
-      </c>
-      <c r="V18" t="n">
-        <v>44.52895</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-77.78169</v>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>13</v>
-      </c>
-      <c r="T19" t="n">
-        <v>325</v>
-      </c>
-      <c r="U19" t="n">
-        <v>42</v>
-      </c>
-      <c r="V19" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -738,35 +738,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,10 +780,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Au 1120g/t, Cu 0.66%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -800,17 +804,17 @@
         <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>44.63956</v>
+        <v>44.55039</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.55477999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -820,21 +824,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -843,7 +847,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -865,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -876,23 +880,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T5" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U5" t="n">
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.29559</v>
+        <v>46.30402</v>
       </c>
       <c r="W5" t="n">
-        <v>-83.20277</v>
+        <v>-81.53989</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -902,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -984,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1040,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T7" t="n">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.73856</v>
+        <v>46.29559</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.32056</v>
+        <v>-83.20277</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1066,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1111,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1131,14 +1135,14 @@
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1148,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1193,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1213,14 +1217,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1230,35 +1234,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.4</v>
+        <v>7.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1275,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.52895</v>
+        <v>44.73856</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.78169</v>
+        <v>-76.32056</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1312,21 +1316,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1335,7 +1339,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1357,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.5021</v>
+        <v>44.52895</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61301</v>
+        <v>-77.78169</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1394,30 +1398,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1439,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1450,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>46.23809</v>
+        <v>44.5021</v>
       </c>
       <c r="W12" t="n">
-        <v>-82.11991</v>
+        <v>-77.61301</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1476,21 +1480,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Jayfran-Pipawa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31F04SE00036</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Vardy</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1499,7 +1503,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Nepheline Syenite, Uranium</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1511,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1521,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>7 drill hole(s) nearby · 1984–1988 · Jayfran Enterprises Ltd, Pipawa Expl Ltd</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1530,25 +1534,29 @@
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
+        </is>
+      </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>45.58868</v>
+        <v>45.09484</v>
       </c>
       <c r="W13" t="n">
-        <v>-79.70944</v>
+        <v>-77.76734999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
         </is>
       </c>
     </row>
@@ -1558,35 +1566,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1603,7 +1611,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1623,14 +1631,14 @@
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>48.69799</v>
+        <v>45.58868</v>
       </c>
       <c r="W14" t="n">
-        <v>-93.27513999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1640,21 +1648,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1663,12 +1671,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1685,7 +1693,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1696,23 +1704,269 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
+        <v>49.71016</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-94.40097</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ackerman</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>MDI31C05NE00018</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Deloro</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>12</v>
+      </c>
+      <c r="T16" t="n">
+        <v>300</v>
+      </c>
+      <c r="U16" t="n">
+        <v>43</v>
+      </c>
+      <c r="V16" t="n">
         <v>44.49976</v>
       </c>
-      <c r="W15" t="n">
+      <c r="W16" t="n">
         <v>-77.61284999999999</v>
       </c>
-      <c r="X15" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Reef Point Occurrence</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MDI52C11NW00007</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Windy Point</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Copper, Nickel</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>13</v>
+      </c>
+      <c r="T17" t="n">
+        <v>325</v>
+      </c>
+      <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>48.69799</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-93.27513999999999</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>13</v>
+      </c>
+      <c r="T18" t="n">
+        <v>325</v>
+      </c>
+      <c r="U18" t="n">
+        <v>42</v>
+      </c>
+      <c r="V18" t="n">
+        <v>48.24876</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-89.86754000000001</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
         <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -906,30 +906,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>1.9</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +951,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +962,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T6" t="n">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.63956</v>
+        <v>46.29559</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.55477999999999</v>
+        <v>-83.20277</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -988,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1044,23 +1044,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>46.29559</v>
+        <v>44.63956</v>
       </c>
       <c r="W7" t="n">
-        <v>-83.20277</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1135,14 +1135,14 @@
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1279,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1290,23 +1290,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1316,21 +1316,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.52895</v>
+        <v>44.5021</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.78169</v>
+        <v>-77.61301</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1398,30 +1398,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.5021</v>
+        <v>46.23809</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61301</v>
+        <v>-82.11991</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1480,17 +1480,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jayfran-Pipawa</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31F04SE00036</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Vardy</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1498,24 +1498,24 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nepheline Syenite, Uranium</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
         <v>1</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1984–1988 · Jayfran Enterprises Ltd, Pipawa Expl Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1534,29 +1534,25 @@
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>abuts Egan Chutes Provincial Park Addition (Waterway Class) boundary</t>
-        </is>
-      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>45.09484</v>
+        <v>44.49976</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.76734999999999</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31F04SE00036</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1648,35 +1644,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I15" t="b">
@@ -1693,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1704,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>49.71016</v>
+        <v>48.69799</v>
       </c>
       <c r="W15" t="n">
-        <v>-94.40097</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1726,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1744,7 +1740,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1775,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R L V Ekstrom · tested Gold</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1786,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.49976</v>
+        <v>44.51686</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.62098</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1812,30 +1808,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1857,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1868,23 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>48.69799</v>
+        <v>44.52895</v>
       </c>
       <c r="W17" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1894,30 +1890,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2.8</v>
+        <v>5.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1939,7 +1935,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1950,21 +1946,103 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
+        <v>4</v>
+      </c>
+      <c r="T18" t="n">
+        <v>100</v>
+      </c>
+      <c r="U18" t="n">
+        <v>43</v>
+      </c>
+      <c r="V18" t="n">
+        <v>49.71016</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-94.40097</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
         <v>13</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>325</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>42</v>
       </c>
-      <c r="V18" t="n">
+      <c r="V19" t="n">
         <v>48.24876</v>
       </c>
-      <c r="W18" t="n">
+      <c r="W19" t="n">
         <v>-89.86754000000001</v>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -824,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Zinc, Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -889,14 +889,14 @@
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W5" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -988,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1053,14 +1053,14 @@
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.63956</v>
+        <v>46.30402</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.55477999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1070,21 +1070,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1115,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1126,23 +1126,23 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T8" t="n">
-        <v>325</v>
+        <v>275</v>
       </c>
       <c r="U8" t="n">
         <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1208,23 +1208,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1299,14 +1299,14 @@
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1330,7 +1330,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.5021</v>
+        <v>44.51686</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.61301</v>
+        <v>-77.62098</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
         </is>
       </c>
     </row>
@@ -1398,21 +1398,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>46.23809</v>
+        <v>48.69799</v>
       </c>
       <c r="W12" t="n">
-        <v>-82.11991</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1480,21 +1480,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.49976</v>
+        <v>49.71016</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61284999999999</v>
+        <v>-94.40097</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1562,35 +1562,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I14" t="b">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1627,14 +1627,14 @@
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>45.58868</v>
+        <v>44.5021</v>
       </c>
       <c r="W14" t="n">
-        <v>-79.70944</v>
+        <v>-77.61301</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1644,21 +1644,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>4.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1700,23 +1700,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>48.69799</v>
+        <v>46.23809</v>
       </c>
       <c r="W15" t="n">
-        <v>-93.27513999999999</v>
+        <v>-82.11991</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1726,35 +1726,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,23 +1782,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.51686</v>
+        <v>45.58868</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.62098</v>
+        <v>-79.70944</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1808,21 +1808,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,23 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>44.52895</v>
+        <v>44.49976</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.78169</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1890,21 +1890,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5.7</v>
+        <v>1.4</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1935,7 +1935,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1946,105 +1946,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T18" t="n">
-        <v>100</v>
+        <v>225</v>
       </c>
       <c r="U18" t="n">
         <v>43</v>
       </c>
       <c r="V18" t="n">
-        <v>49.71016</v>
+        <v>44.52895</v>
       </c>
       <c r="W18" t="n">
-        <v>-94.40097</v>
+        <v>-77.78169</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>13</v>
-      </c>
-      <c r="T19" t="n">
-        <v>325</v>
-      </c>
-      <c r="U19" t="n">
-        <v>42</v>
-      </c>
-      <c r="V19" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
         <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -824,30 +824,30 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -869,7 +869,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -889,14 +889,14 @@
         <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>44.63956</v>
+        <v>46.30402</v>
       </c>
       <c r="W5" t="n">
-        <v>-77.55477999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -988,30 +988,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1033,7 +1033,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1053,14 +1053,14 @@
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W7" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1152,21 +1152,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1217,14 +1217,14 @@
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1234,21 +1234,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.5</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1279,7 +1279,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1299,14 +1299,14 @@
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.55883</v>
+        <v>44.62168</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.56963</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1316,30 +1316,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hawk Eye</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C12SE00032</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1361,7 +1361,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1372,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.51686</v>
+        <v>48.69799</v>
       </c>
       <c r="W11" t="n">
-        <v>-77.62098</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1398,35 +1398,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6.5</v>
+        <v>0.9</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1443,7 +1443,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1454,23 +1454,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>48.69799</v>
+        <v>45.58868</v>
       </c>
       <c r="W12" t="n">
-        <v>-93.27513999999999</v>
+        <v>-79.70944</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1480,21 +1480,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1525,7 +1525,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1536,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>100</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>49.71016</v>
+        <v>44.49976</v>
       </c>
       <c r="W13" t="n">
-        <v>-94.40097</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1562,30 +1562,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.3</v>
+        <v>4.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1607,7 +1607,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1618,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.5021</v>
+        <v>46.23809</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.61301</v>
+        <v>-82.11991</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1644,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C12SE00024</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.3</v>
+        <v>0.8</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1689,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Gold, Copper</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1709,14 +1709,14 @@
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>46.23809</v>
+        <v>44.5143</v>
       </c>
       <c r="W15" t="n">
-        <v>-82.11991</v>
+        <v>-77.61444</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
         </is>
       </c>
     </row>
@@ -1726,35 +1726,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1771,7 +1771,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1791,14 +1791,14 @@
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>45.58868</v>
+        <v>44.5021</v>
       </c>
       <c r="W16" t="n">
-        <v>-79.70944</v>
+        <v>-77.61301</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1808,21 +1808,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Belmar Resc Inc, R J Roach · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,23 +1864,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T17" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>44.49976</v>
+        <v>44.52895</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1890,35 +1890,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1.4</v>
+        <v>2.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1935,7 +1935,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1946,23 +1946,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V18" t="n">
-        <v>44.52895</v>
+        <v>48.24876</v>
       </c>
       <c r="W18" t="n">
-        <v>-77.78169</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
         <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -824,21 +824,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Crownbridge</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI41J06NE00046</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Kynoch</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4.5</v>
+        <v>18.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -866,10 +866,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Cu 2.01%</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t>To a depth of 1000 feet, total reserves, including 10 % allowance for dilution, are stated to be 415 000 tons, grading 1.8% Cu, over an average width of 6.5 feet (Northern Miner, May 27, 1965).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -880,23 +884,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>325</v>
+        <v>175</v>
       </c>
       <c r="U5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V5" t="n">
-        <v>46.30402</v>
+        <v>46.4923</v>
       </c>
       <c r="W5" t="n">
-        <v>-81.53989</v>
+        <v>-83.03964000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00046</t>
         </is>
       </c>
     </row>
@@ -906,21 +910,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.9</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -929,7 +933,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -951,7 +955,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -962,23 +966,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>200</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.29559</v>
+        <v>46.30402</v>
       </c>
       <c r="W6" t="n">
-        <v>-83.20277</v>
+        <v>-81.53989</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1044,10 +1048,10 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
@@ -1070,30 +1074,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1115,7 +1119,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1132,17 +1136,17 @@
         <v>275</v>
       </c>
       <c r="U8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V8" t="n">
-        <v>44.73856</v>
+        <v>46.29559</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.32056</v>
+        <v>-83.20277</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1197,7 +1201,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Stewart Lake Resc Inc, Kirkham Flake Graphite Property</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1316,35 +1320,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6.5</v>
+        <v>7.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1361,7 +1365,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1372,23 +1376,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V11" t="n">
-        <v>48.69799</v>
+        <v>44.73856</v>
       </c>
       <c r="W11" t="n">
-        <v>-93.27513999999999</v>
+        <v>-76.32056</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1480,21 +1484,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1525,7 +1529,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1536,23 +1540,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.49976</v>
+        <v>44.52895</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1562,21 +1566,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1585,7 +1589,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1607,7 +1611,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, D Eldona Gold Mines Ltd · tested Copper</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1618,23 +1622,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>46.23809</v>
+        <v>48.69799</v>
       </c>
       <c r="W14" t="n">
-        <v>-82.11991</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1644,30 +1648,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SE00024</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.8</v>
+        <v>4.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1689,7 +1693,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Gold, Copper</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1709,14 +1713,14 @@
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.5143</v>
+        <v>46.23809</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.61444</v>
+        <v>-82.11991</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1771,7 +1775,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R L V Ekstrom · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1782,10 +1786,10 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T16" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
@@ -1808,21 +1812,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1853,7 +1857,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1864,23 +1868,23 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="U17" t="n">
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>44.52895</v>
+        <v>44.49976</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.78169</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>4.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>46.30402</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -824,21 +820,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Crownbridge</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41J06NE00046</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kynoch</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18.8</v>
+        <v>1.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -847,7 +843,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -866,14 +862,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Cu 2.01%</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>To a depth of 1000 feet, total reserves, including 10 % allowance for dilution, are stated to be 415 000 tons, grading 1.8% Cu, over an average width of 6.5 feet (Northern Miner, May 27, 1965).</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -884,23 +876,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="U5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.4923</v>
+        <v>46.29559</v>
       </c>
       <c r="W5" t="n">
-        <v>-83.03964000000001</v>
+        <v>-83.20277</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00046</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -910,30 +902,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -955,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Company Ltd, Teck Expl Ltd · tested Zinc, Copper</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -966,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -992,30 +984,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1037,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1048,23 +1040,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>44.63956</v>
+        <v>44.62168</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.55477999999999</v>
+        <v>-76.56963</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1074,30 +1066,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.9</v>
+        <v>7.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1119,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1136,17 +1128,17 @@
         <v>275</v>
       </c>
       <c r="U8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>46.29559</v>
+        <v>44.73856</v>
       </c>
       <c r="W8" t="n">
-        <v>-83.20277</v>
+        <v>-76.32056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1238,35 +1230,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1283,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1294,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>44.62168</v>
+        <v>44.5021</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.56963</v>
+        <v>-77.61301</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1320,35 +1312,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.7</v>
+        <v>4.3</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1365,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1376,23 +1368,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U11" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.73856</v>
+        <v>46.23809</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.32056</v>
+        <v>-82.11991</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1402,35 +1394,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I12" t="b">
@@ -1447,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1458,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T12" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>45.58868</v>
+        <v>44.49976</v>
       </c>
       <c r="W12" t="n">
-        <v>-79.70944</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1484,35 +1476,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1529,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1540,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>44.52895</v>
+        <v>45.58868</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.78169</v>
+        <v>-79.70944</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1648,30 +1640,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.3</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1693,7 +1685,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1704,23 +1696,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>46.23809</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-82.11991</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1730,35 +1722,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>2.8</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1775,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1792,179 +1784,15 @@
         <v>300</v>
       </c>
       <c r="U16" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V16" t="n">
-        <v>44.5021</v>
+        <v>48.24876</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61301</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X16" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Ackerman</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>MDI31C05NE00018</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Deloro</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, R J Roach · tested Gold</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
-        <v>12</v>
-      </c>
-      <c r="T17" t="n">
-        <v>300</v>
-      </c>
-      <c r="U17" t="n">
-        <v>43</v>
-      </c>
-      <c r="V17" t="n">
-        <v>44.49976</v>
-      </c>
-      <c r="W17" t="n">
-        <v>-77.61284999999999</v>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I18" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>13</v>
-      </c>
-      <c r="T18" t="n">
-        <v>325</v>
-      </c>
-      <c r="U18" t="n">
-        <v>42</v>
-      </c>
-      <c r="V18" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X18" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T3" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W3" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,12 +761,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,10 +780,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Au 1120g/t, Cu 0.66%</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Zinc, Copper</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -800,17 +804,17 @@
         <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>46.30402</v>
+        <v>44.55039</v>
       </c>
       <c r="W4" t="n">
-        <v>-81.53989</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -820,21 +824,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Crownbridge</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI41J06NE00046</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Kynoch</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1.9</v>
+        <v>18.8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -843,7 +847,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -862,10 +866,14 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Cu 2.01%</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>To a depth of 1000 feet, total reserves, including 10 % allowance for dilution, are stated to be 415 000 tons, grading 1.8% Cu, over an average width of 6.5 feet (Northern Miner, May 27, 1965).</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -876,23 +884,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T5" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="U5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="V5" t="n">
-        <v>46.29559</v>
+        <v>46.4923</v>
       </c>
       <c r="W5" t="n">
-        <v>-83.20277</v>
+        <v>-83.03964000000001</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00046</t>
         </is>
       </c>
     </row>
@@ -902,30 +910,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -947,7 +955,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -958,23 +966,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.63956</v>
+        <v>46.30402</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.55477999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -984,30 +992,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1029,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1040,23 +1048,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T7" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.62168</v>
+        <v>44.63956</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.56963</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -1066,30 +1074,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>7.7</v>
+        <v>1.9</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1111,7 +1119,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1128,17 +1136,17 @@
         <v>275</v>
       </c>
       <c r="U8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="V8" t="n">
-        <v>44.73856</v>
+        <v>46.29559</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.32056</v>
+        <v>-83.20277</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -1230,35 +1238,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.3</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1275,7 +1283,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1286,23 +1294,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T10" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.5021</v>
+        <v>44.62168</v>
       </c>
       <c r="W10" t="n">
-        <v>-77.61301</v>
+        <v>-76.56963</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1312,35 +1320,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4.3</v>
+        <v>7.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I11" t="b">
@@ -1357,7 +1365,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1368,23 +1376,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="U11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="V11" t="n">
-        <v>46.23809</v>
+        <v>44.73856</v>
       </c>
       <c r="W11" t="n">
-        <v>-82.11991</v>
+        <v>-76.32056</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1402,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1408,7 +1416,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1417,7 +1425,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1439,7 +1447,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R L V Ekstrom, Unknown · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1459,14 +1467,14 @@
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.49976</v>
+        <v>44.5021</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1476,35 +1484,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1521,7 +1529,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1532,23 +1540,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>325</v>
+        <v>100</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>45.58868</v>
+        <v>49.71016</v>
       </c>
       <c r="W13" t="n">
-        <v>-79.70944</v>
+        <v>-94.40097</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1558,30 +1566,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1603,7 +1611,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1614,23 +1622,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>48.69799</v>
+        <v>44.52895</v>
       </c>
       <c r="W14" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1640,30 +1648,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>6.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1685,7 +1693,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1696,23 +1704,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>48.69799</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1722,35 +1730,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1767,7 +1775,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R L V Ekstrom, Unknown · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1784,15 +1792,261 @@
         <v>300</v>
       </c>
       <c r="U16" t="n">
+        <v>43</v>
+      </c>
+      <c r="V16" t="n">
+        <v>44.49976</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-77.61284999999999</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rock Brook Resources Property</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>MDI31E12SE00004</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Oranmore</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Other metallic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Calcite</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Deposit</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>13</v>
+      </c>
+      <c r="T17" t="n">
+        <v>325</v>
+      </c>
+      <c r="U17" t="n">
+        <v>43</v>
+      </c>
+      <c r="V17" t="n">
+        <v>45.58868</v>
+      </c>
+      <c r="W17" t="n">
+        <v>-79.70944</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Massey</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MDI41J01NE00008</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Massey</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Copper</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Copper, Gold, Silver</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Past Producing Mine (Low Tonnage)</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="n">
+        <v>225</v>
+      </c>
+      <c r="U18" t="n">
+        <v>43</v>
+      </c>
+      <c r="V18" t="n">
+        <v>46.23809</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-82.11991</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>13</v>
+      </c>
+      <c r="T19" t="n">
+        <v>325</v>
+      </c>
+      <c r="U19" t="n">
         <v>42</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V19" t="n">
         <v>48.24876</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W19" t="n">
         <v>-89.86754000000001</v>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -652,21 +652,21 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Barry Occurrence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C11SW00038</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Actinolite</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -675,7 +675,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Gold</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -696,12 +696,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Cu 3.50%</t>
+          <t>Au 1120g/t, Cu 0.66%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -712,23 +712,23 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T3" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U3" t="n">
         <v>56</v>
       </c>
       <c r="V3" t="n">
-        <v>46.28991</v>
+        <v>44.55039</v>
       </c>
       <c r="W3" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.36235000000001</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
         </is>
       </c>
     </row>
@@ -738,21 +738,21 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Barry Occurrence</t>
+          <t>Glagoma</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI31C11SW00038</t>
+          <t>MDI41J06SE00003</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Actinolite</t>
+          <t>Iron Bridge</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper, Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Au 1120g/t, Cu 0.66%</t>
+          <t>Cu 3.50%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t xml:space="preserve">This is exposed in a road cut on Hastings Co Rd 20, 1.1 km N of Hwy 7 (an 80 ft wide zone) Mineralization consists of pods of pyrite and arsenopyrite ( Lithology Lithology Data Rock Type Rank Composition Texture Relationship Amphibolite 1 Foliated Host Vein 2 Quartz-carbonate Breccia Host Mineralization Mineralization and Alteration Rank Mineral Name Class Economic Mineral Type Alteration Mineral Type Alteration Ranking Alteration Intensity Alteration Style 6 Garnet Economic 1 Gold Economic Ore 2 Arsenopyrite Economic Ore 3 Pyrrhotite Economic Ore 4 Pyrite Economic Ore 5 Chalcopyrite Economic </t>
+          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +798,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="T4" t="n">
-        <v>325</v>
+        <v>225</v>
       </c>
       <c r="U4" t="n">
         <v>56</v>
       </c>
       <c r="V4" t="n">
-        <v>44.55039</v>
+        <v>46.28991</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.36235000000001</v>
+        <v>-83.20480999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C11SW00038</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
         </is>
       </c>
     </row>
@@ -910,30 +910,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4.5</v>
+        <v>0.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -955,7 +955,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -966,23 +966,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="T6" t="n">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>46.30402</v>
+        <v>44.63956</v>
       </c>
       <c r="W6" t="n">
-        <v>-81.53989</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -992,30 +992,30 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1037,7 +1037,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1048,23 +1048,23 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T7" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U7" t="n">
         <v>48</v>
       </c>
       <c r="V7" t="n">
-        <v>44.63956</v>
+        <v>46.30402</v>
       </c>
       <c r="W7" t="n">
-        <v>-77.55477999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1119,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Glagoma Copper Mines Ltd, Principle Strategic Min/Mid Pines · tested Copper</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1156,21 +1156,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4.5</v>
+        <v>7.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1201,7 +1201,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1212,23 +1212,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T9" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.55883</v>
+        <v>44.73856</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.57349000000001</v>
+        <v>-76.32056</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1238,21 +1238,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1283,7 +1283,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1303,14 +1303,14 @@
         <v>46</v>
       </c>
       <c r="V10" t="n">
-        <v>44.62168</v>
+        <v>44.55883</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.56963</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1320,21 +1320,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1365,7 +1365,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1376,23 +1376,23 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T11" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U11" t="n">
         <v>46</v>
       </c>
       <c r="V11" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1402,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1447,7 +1447,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R L V Ekstrom, Unknown · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1467,14 +1467,14 @@
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.5021</v>
+        <v>44.49976</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61301</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1529,7 +1529,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1566,30 +1566,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI41J01NE00008</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Massey</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1.4</v>
+        <v>4.3</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Gold, Silver</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1611,7 +1611,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1622,23 +1622,23 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="n">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="U14" t="n">
         <v>43</v>
       </c>
       <c r="V14" t="n">
-        <v>44.52895</v>
+        <v>46.23809</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.78169</v>
+        <v>-82.11991</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
         </is>
       </c>
     </row>
@@ -1648,30 +1648,30 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.5</v>
+        <v>1.4</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1693,7 +1693,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1704,23 +1704,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T15" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>48.69799</v>
+        <v>44.52895</v>
       </c>
       <c r="W15" t="n">
-        <v>-93.27513999999999</v>
+        <v>-77.78169</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1775,7 +1775,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · R L V Ekstrom, Unknown · tested Gold</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1795,14 +1795,14 @@
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.49976</v>
+        <v>44.5021</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.61301</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1894,21 +1894,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI41J01NE00008</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Massey</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.3</v>
+        <v>6.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Gold, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1939,7 +1939,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1950,23 +1950,23 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T18" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U18" t="n">
         <v>43</v>
       </c>
       <c r="V18" t="n">
-        <v>46.23809</v>
+        <v>48.69799</v>
       </c>
       <c r="W18" t="n">
-        <v>-82.11991</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J01NE00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1976,35 +1976,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Silver Mountain East</t>
+          <t>Hawk Eye</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MDI52A04NW00006</t>
+          <t>MDI31C12SE00032</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Silver Mountain</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2.8</v>
+        <v>0.6</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I19" t="b">
@@ -2021,7 +2021,7 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2032,21 +2032,103 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="n">
+        <v>200</v>
+      </c>
+      <c r="U19" t="n">
+        <v>43</v>
+      </c>
+      <c r="V19" t="n">
+        <v>44.51686</v>
+      </c>
+      <c r="W19" t="n">
+        <v>-77.62098</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Silver Mountain East</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>MDI52A04NW00006</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Silver Mountain</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Silver</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Past Producing Mine</t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>no tonnage on record</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="n">
         <v>13</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>325</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>42</v>
       </c>
-      <c r="V19" t="n">
+      <c r="V20" t="n">
         <v>48.24876</v>
       </c>
-      <c r="W19" t="n">
+      <c r="W20" t="n">
         <v>-89.86754000000001</v>
       </c>
-      <c r="X19" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>

--- a/site/on_leads.xlsx
+++ b/site/on_leads.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X20"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -738,35 +738,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Glagoma</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MDI41J06SE00003</t>
+          <t>MDI31C12NE00021</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Iron Bridge</t>
+          <t>Bannockburn</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="I4" t="b">
@@ -780,14 +780,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Cu 3.50%</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>At the western end a continuous surface showing for a length of 150 feet averages 3.5% copper across a width of four feet. A sample taken across the vein, from the end of the shaft a few feet below the surface assayed 5.3% copper across a width of five feet.</t>
+          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -798,23 +794,23 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="T4" t="n">
-        <v>225</v>
+        <v>325</v>
       </c>
       <c r="U4" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="V4" t="n">
-        <v>46.28991</v>
+        <v>44.63956</v>
       </c>
       <c r="W4" t="n">
-        <v>-83.20480999999999</v>
+        <v>-77.55477999999999</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00003</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
         </is>
       </c>
     </row>
@@ -824,21 +820,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Crownbridge</t>
+          <t>Principle Strategic Minerals Prospect</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MDI41J06NE00046</t>
+          <t>MDI41J06SE00050</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Kynoch</t>
+          <t>Patton</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>18.8</v>
+        <v>1.9</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -847,7 +843,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Copper, Silver</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -866,14 +862,10 @@
           <t>no tonnage on record</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Cu 2.01%</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>To a depth of 1000 feet, total reserves, including 10 % allowance for dilution, are stated to be 415 000 tons, grading 1.8% Cu, over an average width of 6.5 feet (Northern Miner, May 27, 1965).</t>
+          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -884,23 +876,23 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T5" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="U5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="V5" t="n">
-        <v>46.4923</v>
+        <v>46.29559</v>
       </c>
       <c r="W5" t="n">
-        <v>-83.03964000000001</v>
+        <v>-83.20277</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06NE00046</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
         </is>
       </c>
     </row>
@@ -910,30 +902,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Fensom</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MDI31C12NE00021</t>
+          <t>MDI41I05SE00067</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bannockburn</t>
+          <t>Nairn Centre</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.5</v>
+        <v>4.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper, Zinc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -955,7 +947,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1985–1986 · Mono Gold Mines Inc · tested Gold</t>
+          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -966,23 +958,23 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="T6" t="n">
-        <v>300</v>
+        <v>325</v>
       </c>
       <c r="U6" t="n">
         <v>48</v>
       </c>
       <c r="V6" t="n">
-        <v>44.63956</v>
+        <v>46.30402</v>
       </c>
       <c r="W6" t="n">
-        <v>-77.55477999999999</v>
+        <v>-81.53989</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12NE00021</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
         </is>
       </c>
     </row>
@@ -992,17 +984,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Fensom</t>
+          <t>Kirkham Graphite Property</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MDI41I05SE00067</t>
+          <t>MDI31C10SE00023</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Nairn Centre</t>
+          <t>Glendower</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1010,12 +1002,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Copper, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1037,7 +1029,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>22 drill hole(s) nearby · 1952–1953 · Teck Expl Ltd, Teck Expl Company Ltd · tested Copper, Zinc</t>
+          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1054,17 +1046,17 @@
         <v>325</v>
       </c>
       <c r="U7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V7" t="n">
-        <v>46.30402</v>
+        <v>44.55883</v>
       </c>
       <c r="W7" t="n">
-        <v>-81.53989</v>
+        <v>-76.57349000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41I05SE00067</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
         </is>
       </c>
     </row>
@@ -1074,30 +1066,30 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Principle Strategic Minerals Prospect</t>
+          <t>Timmins Mine</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MDI41J06SE00050</t>
+          <t>MDI31C09NW00013</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Patton</t>
+          <t>Stanleyville</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1.9</v>
+        <v>7.7</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Copper, Silver</t>
+          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1119,7 +1111,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>16 drill hole(s) nearby · 1955–1957 · Principle Strategic Min/Mid Pines, Glagoma Copper Mines Ltd · tested Copper</t>
+          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1136,17 +1128,17 @@
         <v>275</v>
       </c>
       <c r="U8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="V8" t="n">
-        <v>46.29559</v>
+        <v>44.73856</v>
       </c>
       <c r="W8" t="n">
-        <v>-83.20277</v>
+        <v>-76.32056</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI41J06SE00050</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
         </is>
       </c>
     </row>
@@ -1156,21 +1148,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Timmins Mine</t>
+          <t>Meadow Lake Zone</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MDI31C09NW00013</t>
+          <t>MDI31C10SE00205</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Stanleyville</t>
+          <t>Bedford</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.7</v>
+        <v>0.7</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1179,7 +1171,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Graphite, Copper, Iron, Nickel, Zinc</t>
+          <t>Graphite</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1201,7 +1193,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>The East and Central Zones were 91 m and 137 m in length and averaged 3.4 m @ 7.6% C and 3.9 m @8.4% C, The ore zone is comprised of several individual zones up to 610 m in length.</t>
+          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1212,23 +1204,23 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T9" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U9" t="n">
         <v>46</v>
       </c>
       <c r="V9" t="n">
-        <v>44.73856</v>
+        <v>44.62168</v>
       </c>
       <c r="W9" t="n">
-        <v>-76.32056</v>
+        <v>-76.56963</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C09NW00013</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
         </is>
       </c>
     </row>
@@ -1238,35 +1230,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kirkham Graphite Property</t>
+          <t>Ledyard</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MDI31C10SE00023</t>
+          <t>MDI31C12SW00008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Glendower</t>
+          <t>Cordova Mines</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4.5</v>
+        <v>1.4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I10" t="b">
@@ -1283,7 +1275,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>118 drill hole(s) nearby · 1987–1988 · Kirkham Flake Graphite Property, Stewart Lake Resc Inc</t>
+          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1294,23 +1286,23 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>325</v>
+        <v>250</v>
       </c>
       <c r="U10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V10" t="n">
-        <v>44.55883</v>
+        <v>44.52895</v>
       </c>
       <c r="W10" t="n">
-        <v>-76.57349000000001</v>
+        <v>-77.78169</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00023</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
         </is>
       </c>
     </row>
@@ -1320,30 +1312,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Meadow Lake Zone</t>
+          <t>Rock Brook Resources Property</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MDI31C10SE00205</t>
+          <t>MDI31E12SE00004</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bedford</t>
+          <t>Oranmore</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Other metallic</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Graphite</t>
+          <t>Calcite</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1365,7 +1357,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>17 drill hole(s) nearby · 1997–1999 · Graphite Mountain Inc</t>
+          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1382,17 +1374,17 @@
         <v>325</v>
       </c>
       <c r="U11" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="V11" t="n">
-        <v>44.62168</v>
+        <v>45.58868</v>
       </c>
       <c r="W11" t="n">
-        <v>-76.56963</v>
+        <v>-79.70944</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C10SE00205</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
         </is>
       </c>
     </row>
@@ -1402,12 +1394,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ackerman</t>
+          <t>Cook</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MDI31C05NE00018</t>
+          <t>MDI31C12SE00024</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1416,7 +1408,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1447,7 +1439,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>11 drill hole(s) nearby · 1973 · Sudbury Contact Mines Ltd · tested Copper, Gold</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1458,23 +1450,23 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="T12" t="n">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="U12" t="n">
         <v>43</v>
       </c>
       <c r="V12" t="n">
-        <v>44.49976</v>
+        <v>44.5143</v>
       </c>
       <c r="W12" t="n">
-        <v>-77.61284999999999</v>
+        <v>-77.61444</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00024</t>
         </is>
       </c>
     </row>
@@ -1484,35 +1476,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sultana</t>
+          <t>Reef Point Occurrence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MDI52E09NW00011</t>
+          <t>MDI52C11NW00007</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Longbow Lake</t>
+          <t>Windy Point</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Copper</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gold, Molybdenum, Silver</t>
+          <t>Copper, Nickel</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Past Producing Mine</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -1529,7 +1521,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>7 drill hole(s) nearby · 1974–1981 · Ed Roberecki, Minaki Gold Mines Ltd · tested Copper, Zinc</t>
+          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
@@ -1540,23 +1532,23 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T13" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="U13" t="n">
         <v>43</v>
       </c>
       <c r="V13" t="n">
-        <v>49.71016</v>
+        <v>48.69799</v>
       </c>
       <c r="W13" t="n">
-        <v>-94.40097</v>
+        <v>-93.27513999999999</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1603,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>12 drill hole(s) nearby · 1955–2005 · Terex Resc Ltd, Donalda Mines Ltd · tested Copper</t>
+          <t>12 drill hole(s) nearby · 1955–2005 · Donalda Mines Ltd, J Gutcher · tested Copper</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -1648,21 +1640,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ledyard</t>
+          <t>Dean and Williams</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MDI31C12SW00008</t>
+          <t>MDI31C12SE00029</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cordova Mines</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1671,7 +1663,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold, Arsenic</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1693,7 +1685,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1987 · Belmar Resources Inc</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -1704,23 +1696,23 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T15" t="n">
-        <v>250</v>
+        <v>325</v>
       </c>
       <c r="U15" t="n">
         <v>43</v>
       </c>
       <c r="V15" t="n">
-        <v>44.52895</v>
+        <v>44.5021</v>
       </c>
       <c r="W15" t="n">
-        <v>-77.78169</v>
+        <v>-77.61301</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SW00008</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
         </is>
       </c>
     </row>
@@ -1730,21 +1722,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Dean and Williams</t>
+          <t>Sultana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MDI31C12SE00029</t>
+          <t>MDI52E09NW00011</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Deloro</t>
+          <t>Longbow Lake</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1.3</v>
+        <v>5.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1753,12 +1745,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gold, Arsenic</t>
+          <t>Gold, Molybdenum, Silver</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I16" t="b">
@@ -1775,7 +1767,7 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>6 drill hole(s) nearby · 1960–1985 · Unknown, Belmar Resc Inc · tested Gold</t>
+          <t>7 drill hole(s) nearby · 1974–1981 · Minaki Gold Mines Ltd, Ed Roberecki · tested Copper, Zinc</t>
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
@@ -1786,23 +1778,23 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="U16" t="n">
         <v>43</v>
       </c>
       <c r="V16" t="n">
-        <v>44.5021</v>
+        <v>49.71016</v>
       </c>
       <c r="W16" t="n">
-        <v>-77.61301</v>
+        <v>-94.40097</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00029</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52E09NW00011</t>
         </is>
       </c>
     </row>
@@ -1812,35 +1804,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Rock Brook Resources Property</t>
+          <t>Ackerman</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MDI31E12SE00004</t>
+          <t>MDI31C05NE00018</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Oranmore</t>
+          <t>Deloro</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Other metallic</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Calcite</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Past Producing Mine (Low Tonnage)</t>
         </is>
       </c>
       <c r="I17" t="b">
@@ -1857,7 +1849,7 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>1 drill hole(s) nearby · 1973 · Cons Can Faraday Ltd</t>
+          <t>6 drill hole(s) nearby · 1960–1985 · R J Roach, R L V Ekstrom · tested Gold</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -1877,14 +1869,14 @@
         <v>43</v>
       </c>
       <c r="V17" t="n">
-        <v>45.58868</v>
+        <v>44.49976</v>
       </c>
       <c r="W17" t="n">
-        <v>-79.70944</v>
+        <v>-77.61284999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31E12SE00004</t>
+          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C05NE00018</t>
         </is>
       </c>
     </row>
@@ -1894,35 +1886,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Reef Point Occurrence</t>
+          <t>Silver Mountain East</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MDI52C11NW00007</t>
+          <t>MDI52A04NW00006</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Windy Point</t>
+          <t>Silver Mountain</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6.5</v>
+        <v>2.8</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Copper</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Copper, Nickel</t>
+          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
+          <t>Past Producing Mine</t>
         </is>
       </c>
       <c r="I18" t="b">
@@ -1939,7 +1931,7 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2 drill hole(s) nearby · 1960 · Bill Croome</t>
+          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
@@ -1956,179 +1948,15 @@
         <v>325</v>
       </c>
       <c r="U18" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="V18" t="n">
-        <v>48.69799</v>
+        <v>48.24876</v>
       </c>
       <c r="W18" t="n">
-        <v>-93.27513999999999</v>
+        <v>-89.86754000000001</v>
       </c>
       <c r="X18" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52C11NW00007</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Hawk Eye</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>MDI31C12SE00032</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Deloro</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Gold</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Past Producing Mine (Low Tonnage)</t>
-        </is>
-      </c>
-      <c r="I19" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>14 drill hole(s) nearby · 1973–1984 · Goldbrook Expl Ltd, Sudbury Contact Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="n">
-        <v>8</v>
-      </c>
-      <c r="T19" t="n">
-        <v>200</v>
-      </c>
-      <c r="U19" t="n">
-        <v>43</v>
-      </c>
-      <c r="V19" t="n">
-        <v>44.51686</v>
-      </c>
-      <c r="W19" t="n">
-        <v>-77.62098</v>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI31C12SE00032</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Silver Mountain East</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>MDI52A04NW00006</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Silver Mountain</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Silver</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Silver, Barite, Calcite, Copper, Fluorite, Lead, Zinc</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Past Producing Mine</t>
-        </is>
-      </c>
-      <c r="I20" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" t="b">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>no tonnage on record</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2 drill hole(s) nearby · 1947 · Mcwilliams Beardmore Mines Ltd</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="n">
-        <v>13</v>
-      </c>
-      <c r="T20" t="n">
-        <v>325</v>
-      </c>
-      <c r="U20" t="n">
-        <v>42</v>
-      </c>
-      <c r="V20" t="n">
-        <v>48.24876</v>
-      </c>
-      <c r="W20" t="n">
-        <v>-89.86754000000001</v>
-      </c>
-      <c r="X20" t="inlineStr">
         <is>
           <t>https://www.geologyontario.mines.gov.on.ca/persistent-linking?mineral-inventory=MDI52A04NW00006</t>
         </is>
